--- a/translation/review/000scriptAKYO_0025A.xlsx
+++ b/translation/review/000scriptAKYO_0025A.xlsx
@@ -31,19 +31,19 @@
     <t>If anyone out there agrees with me, I seriously think that we could be best friends.</t>
   </si>
   <si>
-    <t>Si alguien por ahí está de acuerdo conmigo, en serio creo que podríamos ser mejores amigos.</t>
+    <t>Si alguien por ahí está de acuerdo conmigo, en＿serio creo que podríamos ser mejores amigos.</t>
   </si>
   <si>
     <t>This extremely arrogant girl's name is Kousaka Kirino, my sister who has nothing in common with me.</t>
   </si>
   <si>
-    <t>El nombre de esta chica extremadamente arrogante es Kousaka Kirino, mi hermana con quien no tengo nada en común.</t>
+    <t>El nombre de esta chica extremadamente＿arrogante es Kousaka Kirino, mi hermana con＿quien no tengo nada en común.</t>
   </si>
   <si>
     <t>My sister is, unlike the fairly mediocre me, an outstanding person.</t>
   </si>
   <si>
-    <t>Mi hermana es, a diferencia de mí, que soy bastante mediocre, una persona sobresaliente.</t>
+    <t>Mi hermana es, a diferencia de mí, que soy＿bastante mediocre, una persona sobresaliente.</t>
   </si>
   <si>
     <t>...However, this is just a "facade".</t>
@@ -73,7 +73,7 @@
     <t>Contrary to her appearance, this extraordinarily cute girl is...</t>
   </si>
   <si>
-    <t>Contrario a su apariencia, esta chica extraordinariamente linda es...</t>
+    <t>Contrario a su apariencia, esta chica＿extraordinariamente linda es...</t>
   </si>
   <si>
     <t>When she's full of herself...</t>
@@ -85,7 +85,7 @@
     <t>When that time comes, she behaves exactly like a princess.</t>
   </si>
   <si>
-    <t>Cuando llega ese momento, se comporta exactamente como una princesa.</t>
+    <t>Cuando llega ese momento, se comporta＿exactamente como una princesa.</t>
   </si>
   <si>
     <t>I'll let you know... how I have become revulsed so.</t>
@@ -103,13 +103,13 @@
     <t>She loves dating sims, which are commonly referred to as galge!</t>
   </si>
   <si>
-    <t>¡Le encantan los simuladores de citas, comúnmente conocidos como galge!</t>
+    <t>¡Le encantan los simuladores de citas,＿comúnmente conocidos como galge!</t>
   </si>
   <si>
     <t>Especially "sister-related" ones. She has no self-control whatsoever and has already collected many of them.</t>
   </si>
   <si>
-    <t>Especialmente los «relacionados con hermanitas». No tiene autocontrol alguno y ya ha coleccionado muchos.</t>
+    <t>Especialmente los «relacionados con hermanitas».＿No tiene autocontrol alguno y ya ha＿coleccionado muchos.</t>
   </si>
   <si>
     <t>Kirino</t>
@@ -118,7 +118,7 @@
     <t>...Disgusting. Could it be that you're having some strange thoughts by looking at me?</t>
   </si>
   <si>
-    <t>...Qué asco. ¿Será que tienes pensamientos raros al mirarme?</t>
+    <t>...Qué asco. ¿Será que tienes pensamientos＿raros al mirarme?</t>
   </si>
   <si>
     <t>My sister and her "reverse side's friends",</t>
@@ -130,7 +130,7 @@
     <t>share the same interest, comrades as we call it.</t>
   </si>
   <si>
-    <t>comparten el mismo interés, camaradas como las llamamos.</t>
+    <t>comparten el mismo interés, camaradas como las＿llamamos.</t>
   </si>
   <si>
     <t>Saori</t>
@@ -139,7 +139,7 @@
     <t>Haha, it's great that you've cleared up that misunderstanding with Kiririn-shi, isn't it, Kyousuke-shi?</t>
   </si>
   <si>
-    <t>Jaja, qué bueno que hayas aclarado ese malentendido con Kiririn-shi, ¿no, Kyousuke-shi?</t>
+    <t>Jaja, qué bueno que hayas aclarado ese＿malentendido con Kiririn-shi, ¿no,＿Kyousuke-shi?</t>
   </si>
   <si>
     <t>Ah, all thanks to you.</t>
@@ -151,7 +151,7 @@
     <t>This girl's advice have always saved me.</t>
   </si>
   <si>
-    <t>Los consejos de esta chica siempre me han salvado.</t>
+    <t>Los consejos de esta chica siempre me han＿salvado.</t>
   </si>
   <si>
     <t>Kuroneko</t>
@@ -160,19 +160,19 @@
     <t>I guess it's about time for this sibling quarrel to end...?</t>
   </si>
   <si>
-    <t>Supongo que ya es hora de que termine esta pelea entre hermanos...?</t>
+    <t>Supongo que ya es hora de que termine esta＿pelea entre hermanos...?</t>
   </si>
   <si>
     <t>How long does this girl plan to relax on my bed?</t>
   </si>
   <si>
-    <t>¿Cuánto tiempo planea esta chica relajarse en mi cama?</t>
+    <t>¿Cuánto tiempo planea esta chica relajarse en mi＿cama?</t>
   </si>
   <si>
     <t>Don't go around lying on someone else's bed!</t>
   </si>
   <si>
-    <t>¡No andes recostándote en la cama de otra persona!</t>
+    <t>¡No andes recostándote en la cama de otra＿persona!</t>
   </si>
   <si>
     <t>It's not your bed, is it? Why are you angry?</t>
@@ -214,7 +214,7 @@
     <t>I wasn't able to ask due to the ruckus earlier on...</t>
   </si>
   <si>
-    <t>No pude preguntar debido al alboroto de antes...</t>
+    <t>No pude preguntar debido al alboroto de＿antes...</t>
   </si>
   <si>
     <t>For what reason hath thou gathered us for this day?</t>
@@ -238,7 +238,7 @@
     <t>Ehehe, in fact... I have something awesome to tell you all!</t>
   </si>
   <si>
-    <t>Ejeje, de hecho... ¡Tengo algo increíble que contarles!</t>
+    <t>Ejeje, de hecho... ¡Tengo algo increíble que＿contarles!</t>
   </si>
   <si>
     <t>Kyousuke</t>
@@ -250,25 +250,25 @@
     <t>I've learned my lesson. According to the experiences I have had up to now...</t>
   </si>
   <si>
-    <t>He aprendido la lección. Según las experiencias que he tenido hasta ahora...</t>
+    <t>He aprendido la lección. Según las experiencias＿que he tenido hasta ahora...</t>
   </si>
   <si>
     <t>At this point, some event is going to disrupt my lovely "ordinary life".</t>
   </si>
   <si>
-    <t>En este punto, algún evento va a perturbar mi hermosa «vida ordinaria».</t>
+    <t>En este punto, algún evento va a perturbar mi＿hermosa «vida ordinaria».</t>
   </si>
   <si>
     <t>It became like that the moment I accepted the "life counseling".</t>
   </si>
   <si>
-    <t>Se volvió así en el momento en que acepté la «orientación en la vida».</t>
+    <t>Se volvió así en el momento en que acepté la＿«orientación en la vida».</t>
   </si>
   <si>
     <t>The ones that caused the disruption were, of course, Kirino and her "reverse side's friends."</t>
   </si>
   <si>
-    <t>Los que causaron la perturbación fueron, por supuesto, Kirino y las «amigas de su lado oculto».</t>
+    <t>Los que causaron la perturbación fueron, por＿supuesto, Kirino y las «amigas de su lado＿oculto».</t>
   </si>
   <si>
     <t>What kind of tempest awaits me this time?</t>
@@ -286,7 +286,7 @@
     <t>To even be looking forward to it... It has to be my imagination.</t>
   </si>
   <si>
-    <t>Incluso estar esperándolo con ansias... Tiene que ser mi imaginación.</t>
+    <t>Incluso estar esperándolo con ansias... Tiene que＿ser mi imaginación.</t>
   </si>
 </sst>
 </file>
